--- a/data/trans_dic/P16-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas</t>
+          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,69; 23,64</t>
+          <t>16,59; 23,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,29; 31,56</t>
+          <t>23,62; 32,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,51; 26,67</t>
+          <t>18,12; 26,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,36; 33,04</t>
+          <t>18,0; 33,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,01; 42,54</t>
+          <t>33,64; 42,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,42; 53,6</t>
+          <t>43,77; 53,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,43; 47,97</t>
+          <t>38,08; 47,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30,78; 45,11</t>
+          <t>31,18; 45,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25,99; 31,58</t>
+          <t>25,87; 31,33</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34,55; 41,49</t>
+          <t>34,42; 41,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,96; 35,76</t>
+          <t>29,35; 35,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,09; 35,49</t>
+          <t>25,32; 36,28</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,08; 23,51</t>
+          <t>17,12; 23,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,24; 36,35</t>
+          <t>29,22; 36,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,81; 36,34</t>
+          <t>28,84; 36,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27,74; 39,91</t>
+          <t>28,09; 40,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,56; 47,7</t>
+          <t>39,05; 47,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,19; 62,23</t>
+          <t>54,37; 62,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,74; 51,55</t>
+          <t>43,12; 51,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>44,26; 69,82</t>
+          <t>44,38; 72,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,43; 33,3</t>
+          <t>28,44; 33,43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41,98; 47,75</t>
+          <t>42,26; 47,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37,03; 43,01</t>
+          <t>37,08; 42,79</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38,67; 56,78</t>
+          <t>38,54; 58,67</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24,05; 30,99</t>
+          <t>23,73; 30,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33,17; 40,83</t>
+          <t>33,62; 41,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32,97; 40,44</t>
+          <t>32,77; 40,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35,18; 43,88</t>
+          <t>34,95; 43,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>41,15; 48,87</t>
+          <t>41,81; 49,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>56,74; 64,67</t>
+          <t>56,84; 64,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,75; 55,5</t>
+          <t>47,54; 55,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46,75; 54,02</t>
+          <t>46,96; 53,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34,22; 39,36</t>
+          <t>34,05; 39,48</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46,58; 52,04</t>
+          <t>46,48; 51,99</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41,39; 46,94</t>
+          <t>41,41; 47,05</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>41,98; 47,79</t>
+          <t>42,05; 48,02</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>35,23; 44,62</t>
+          <t>35,45; 44,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43,45; 51,81</t>
+          <t>42,65; 51,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,07; 55,81</t>
+          <t>47,42; 56,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,51; 52,38</t>
+          <t>16,13; 52,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>52,54; 61,2</t>
+          <t>52,42; 60,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,67; 73,44</t>
+          <t>65,21; 73,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,12; 65,49</t>
+          <t>57,04; 64,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>48,8; 63,01</t>
+          <t>48,32; 62,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>44,98; 51,34</t>
+          <t>44,75; 51,53</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55,24; 61,43</t>
+          <t>55,66; 61,48</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53,48; 59,28</t>
+          <t>53,56; 59,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26,8; 56,28</t>
+          <t>29,4; 56,3</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>68,13; 76,89</t>
+          <t>68,49; 76,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>71,08; 79,54</t>
+          <t>70,68; 79,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60,36; 69,42</t>
+          <t>60,6; 69,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66,9; 74,51</t>
+          <t>67,4; 74,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>70,62; 79,1</t>
+          <t>70,77; 79,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>78,63; 86,19</t>
+          <t>78,5; 86,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,47; 83,29</t>
+          <t>75,15; 83,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>72,73; 78,23</t>
+          <t>72,33; 77,67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>70,91; 77,05</t>
+          <t>71,06; 77,11</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76,19; 82,02</t>
+          <t>76,23; 82,11</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69,42; 75,59</t>
+          <t>69,51; 75,79</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>70,74; 75,26</t>
+          <t>70,74; 75,1</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>74,13; 83,54</t>
+          <t>74,7; 83,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>84,63; 91,99</t>
+          <t>84,44; 91,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>79,55; 87,75</t>
+          <t>78,75; 87,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>73,03; 80,25</t>
+          <t>72,8; 80,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>86,63; 92,94</t>
+          <t>86,64; 92,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>88,39; 94,7</t>
+          <t>88,12; 94,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>88,93; 94,4</t>
+          <t>88,42; 94,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>82,32; 95,45</t>
+          <t>82,31; 94,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>82,29; 87,74</t>
+          <t>82,34; 87,77</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>87,65; 92,44</t>
+          <t>87,82; 92,64</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>85,44; 90,43</t>
+          <t>85,4; 90,19</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>79,4; 91,06</t>
+          <t>79,46; 91,73</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>84,83; 92,85</t>
+          <t>84,53; 92,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>89,56; 96,15</t>
+          <t>89,6; 96,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87,48; 94,06</t>
+          <t>87,24; 93,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82,58; 89,28</t>
+          <t>82,87; 89,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>89,92; 96,09</t>
+          <t>89,85; 95,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,42; 98,44</t>
+          <t>94,39; 98,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,35; 97,17</t>
+          <t>92,2; 97,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>89,75; 93,8</t>
+          <t>89,5; 93,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>89,19; 94,0</t>
+          <t>89,26; 94,03</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>93,51; 97,03</t>
+          <t>93,46; 96,97</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91,45; 95,32</t>
+          <t>91,4; 95,25</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,52; 91,15</t>
+          <t>87,85; 91,4</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>38,87; 42,28</t>
+          <t>39,03; 42,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>48,74; 52,14</t>
+          <t>48,51; 52,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48,13; 51,57</t>
+          <t>48,07; 51,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37,87; 53,75</t>
+          <t>38,23; 53,76</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>56,74; 60,35</t>
+          <t>56,87; 60,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>68,64; 71,83</t>
+          <t>68,7; 71,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,99; 66,46</t>
+          <t>63,38; 66,7</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>63,35; 73,24</t>
+          <t>63,1; 71,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>48,45; 50,88</t>
+          <t>48,47; 50,94</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59,2; 61,66</t>
+          <t>59,37; 61,67</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56,35; 58,79</t>
+          <t>56,3; 58,65</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>51,05; 61,46</t>
+          <t>51,84; 61,58</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas</t>
+          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>82440; 116786</t>
+          <t>81952; 117598</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>105522; 142989</t>
+          <t>107012; 146037</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77658; 111882</t>
+          <t>76018; 111236</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>69441; 132162</t>
+          <t>72002; 133986</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>159014; 198862</t>
+          <t>157248; 198328</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>186433; 230124</t>
+          <t>187939; 229218</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>152107; 189830</t>
+          <t>150690; 188818</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>96405; 141283</t>
+          <t>97650; 141944</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>249886; 303706</t>
+          <t>248718; 301250</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>304844; 366091</t>
+          <t>303722; 363565</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>236052; 291543</t>
+          <t>239272; 291924</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>178955; 253131</t>
+          <t>180543; 258723</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>125592; 172912</t>
+          <t>125890; 169890</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>200624; 249465</t>
+          <t>200519; 253427</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>170093; 214607</t>
+          <t>170300; 216388</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>117485; 169031</t>
+          <t>118989; 170236</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>247414; 298383</t>
+          <t>244260; 295660</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>330673; 379770</t>
+          <t>331783; 381640</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>246501; 290495</t>
+          <t>242982; 290265</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>226389; 357137</t>
+          <t>226998; 369320</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>386950; 453246</t>
+          <t>387101; 454910</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>544212; 619054</t>
+          <t>547929; 616204</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>427364; 496397</t>
+          <t>427961; 493859</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>361595; 530964</t>
+          <t>360376; 548565</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>153341; 197625</t>
+          <t>151285; 196821</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>225563; 277670</t>
+          <t>228638; 280091</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>220568; 270608</t>
+          <t>219262; 271446</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>188670; 235371</t>
+          <t>187455; 235041</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>283816; 337086</t>
+          <t>288395; 341060</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>402717; 459043</t>
+          <t>403490; 458874</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>315814; 367079</t>
+          <t>314422; 365169</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>253628; 293017</t>
+          <t>254736; 292812</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>454199; 522514</t>
+          <t>451994; 524054</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>647462; 723221</t>
+          <t>645963; 722578</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>550677; 624464</t>
+          <t>550972; 626012</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>452915; 515530</t>
+          <t>453616; 518093</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>182875; 231637</t>
+          <t>184061; 228949</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>267068; 318449</t>
+          <t>262114; 317482</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>304098; 360553</t>
+          <t>306326; 361943</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>146578; 465039</t>
+          <t>143183; 463355</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>270910; 315584</t>
+          <t>270304; 312237</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>404009; 451846</t>
+          <t>401164; 450962</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>370782; 425074</t>
+          <t>370205; 421583</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>347869; 449165</t>
+          <t>344491; 448413</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>465431; 531258</t>
+          <t>463043; 533198</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>679320; 755503</t>
+          <t>684538; 756149</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>692619; 767774</t>
+          <t>693641; 769296</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>428954; 900858</t>
+          <t>470664; 901229</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>263469; 297333</t>
+          <t>264866; 297362</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>304471; 340702</t>
+          <t>302758; 340360</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>288474; 331765</t>
+          <t>289597; 333658</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>375472; 418200</t>
+          <t>378275; 416846</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>285280; 319556</t>
+          <t>285917; 319593</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>352105; 385961</t>
+          <t>351533; 387406</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>374992; 413822</t>
+          <t>373372; 413441</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>396292; 426279</t>
+          <t>394139; 423231</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>560703; 609266</t>
+          <t>561867; 609684</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>667501; 718639</t>
+          <t>667860; 719421</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>676666; 736798</t>
+          <t>677593; 738738</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>782513; 832487</t>
+          <t>782471; 830667</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>216902; 244414</t>
+          <t>218554; 244351</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>262175; 284976</t>
+          <t>261592; 284306</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>265961; 293380</t>
+          <t>263278; 292499</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>268876; 295438</t>
+          <t>268013; 294607</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>297082; 318725</t>
+          <t>297109; 318872</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>312896; 335248</t>
+          <t>311942; 334730</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>335926; 356602</t>
+          <t>334022; 356630</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>500822; 580657</t>
+          <t>500725; 577322</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>522983; 557613</t>
+          <t>523316; 557781</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>581827; 613596</t>
+          <t>582903; 614951</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608386; 643980</t>
+          <t>608106; 642258</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>775348; 889242</t>
+          <t>775969; 895782</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>178048; 194876</t>
+          <t>177413; 195150</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>223757; 240225</t>
+          <t>223864; 240338</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>224817; 241723</t>
+          <t>224201; 241180</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>233495; 252449</t>
+          <t>234327; 252603</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>300238; 320849</t>
+          <t>300033; 319997</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>367271; 382892</t>
+          <t>367176; 383489</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>369552; 388842</t>
+          <t>368957; 388723</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>381711; 398928</t>
+          <t>380618; 397712</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>484994; 511159</t>
+          <t>485364; 511344</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>597392; 619835</t>
+          <t>597070; 619491</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>600959; 626427</t>
+          <t>600675; 625974</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>619708; 645418</t>
+          <t>622010; 647174</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1273254; 1384974</t>
+          <t>1278406; 1386547</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1667748; 1784240</t>
+          <t>1659947; 1782840</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1633568; 1750301</t>
+          <t>1631591; 1748531</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1310152; 1859567</t>
+          <t>1322592; 1860030</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1917351; 2039467</t>
+          <t>1921725; 2034112</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2440594; 2553846</t>
+          <t>2442542; 2556228</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2232652; 2355591</t>
+          <t>2246478; 2364311</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2317771; 2679727</t>
+          <t>2308673; 2627814</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3224177; 3385897</t>
+          <t>3225281; 3389671</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4130658; 4301986</t>
+          <t>4142304; 4302665</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3910385; 4079246</t>
+          <t>3906636; 4069645</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3634249; 4375000</t>
+          <t>3690438; 4383430</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>31,47%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,59; 23,8</t>
+          <t>16,55; 23,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,62; 32,23</t>
+          <t>23,28; 32,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,12; 26,52</t>
+          <t>18,3; 26,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,0; 33,5</t>
+          <t>18,26; 32,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,64; 42,42</t>
+          <t>33,67; 41,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,77; 53,39</t>
+          <t>43,73; 53,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,08; 47,71</t>
+          <t>38,42; 48,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31,18; 45,32</t>
+          <t>31,8; 45,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25,87; 31,33</t>
+          <t>25,97; 31,74</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34,42; 41,2</t>
+          <t>34,66; 41,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29,35; 35,81</t>
+          <t>29,39; 35,79</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,32; 36,28</t>
+          <t>26,81; 36,77</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>38,43%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,12; 23,1</t>
+          <t>17,31; 22,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,22; 36,93</t>
+          <t>29,14; 36,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,84; 36,65</t>
+          <t>28,83; 36,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28,09; 40,19</t>
+          <t>27,02; 38,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,05; 47,27</t>
+          <t>39,46; 47,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,37; 62,54</t>
+          <t>54,12; 62,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,12; 51,51</t>
+          <t>43,26; 51,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>44,38; 72,2</t>
+          <t>39,04; 48,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,44; 33,43</t>
+          <t>28,29; 33,52</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42,26; 47,53</t>
+          <t>42,18; 47,83</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37,08; 42,79</t>
+          <t>36,65; 42,68</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38,54; 58,67</t>
+          <t>34,5; 42,05</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>43,68%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,73; 30,87</t>
+          <t>23,88; 30,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33,62; 41,19</t>
+          <t>33,43; 41,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32,77; 40,57</t>
+          <t>32,82; 40,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34,95; 43,82</t>
+          <t>33,37; 41,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>41,81; 49,45</t>
+          <t>41,24; 48,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>56,84; 64,65</t>
+          <t>56,91; 64,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,54; 55,21</t>
+          <t>47,86; 55,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46,96; 53,98</t>
+          <t>46,49; 53,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34,05; 39,48</t>
+          <t>34,01; 39,32</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46,48; 51,99</t>
+          <t>46,54; 52,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41,41; 47,05</t>
+          <t>41,58; 46,68</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>42,05; 48,02</t>
+          <t>41,19; 46,41</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>55,78%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>35,45; 44,1</t>
+          <t>35,27; 44,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,65; 51,66</t>
+          <t>43,16; 51,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,42; 56,02</t>
+          <t>47,65; 56,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,13; 52,19</t>
+          <t>46,12; 54,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>52,42; 60,55</t>
+          <t>51,86; 60,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,21; 73,3</t>
+          <t>65,31; 73,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,04; 64,95</t>
+          <t>57,08; 64,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>48,32; 62,9</t>
+          <t>58,21; 64,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>44,75; 51,53</t>
+          <t>45,2; 51,32</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55,66; 61,48</t>
+          <t>55,28; 61,42</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53,56; 59,4</t>
+          <t>53,9; 59,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,4; 56,3</t>
+          <t>53,45; 58,14</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>72,18%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>68,49; 76,9</t>
+          <t>68,15; 77,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>70,68; 79,46</t>
+          <t>70,7; 79,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60,6; 69,81</t>
+          <t>60,6; 69,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67,4; 74,27</t>
+          <t>65,77; 73,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>70,77; 79,11</t>
+          <t>70,66; 79,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>78,5; 86,51</t>
+          <t>79,02; 86,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,15; 83,21</t>
+          <t>75,18; 83,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>72,33; 77,67</t>
+          <t>72,34; 77,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>71,06; 77,11</t>
+          <t>70,8; 77,23</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76,23; 82,11</t>
+          <t>76,15; 81,98</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69,51; 75,79</t>
+          <t>69,07; 75,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>70,74; 75,1</t>
+          <t>69,83; 74,41</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>80,01%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>74,7; 83,52</t>
+          <t>74,16; 83,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>84,44; 91,78</t>
+          <t>84,44; 91,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>78,75; 87,49</t>
+          <t>79,68; 87,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>72,8; 80,02</t>
+          <t>72,98; 80,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>86,64; 92,98</t>
+          <t>86,32; 92,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>88,12; 94,56</t>
+          <t>88,55; 94,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>88,42; 94,41</t>
+          <t>88,17; 94,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>82,31; 94,9</t>
+          <t>80,4; 85,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>82,34; 87,77</t>
+          <t>82,33; 87,85</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>87,82; 92,64</t>
+          <t>87,81; 92,63</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>85,4; 90,19</t>
+          <t>85,48; 90,27</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>79,46; 91,73</t>
+          <t>77,59; 82,17</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,31%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>84,53; 92,98</t>
+          <t>84,89; 92,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>89,6; 96,19</t>
+          <t>89,9; 96,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87,24; 93,85</t>
+          <t>87,42; 94,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82,87; 89,34</t>
+          <t>81,91; 89,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>89,85; 95,83</t>
+          <t>90,08; 95,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,39; 98,59</t>
+          <t>94,32; 98,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,2; 97,14</t>
+          <t>92,41; 97,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>89,5; 93,52</t>
+          <t>89,08; 93,26</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>89,26; 94,03</t>
+          <t>89,13; 93,91</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>93,46; 96,97</t>
+          <t>93,54; 97,07</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91,4; 95,25</t>
+          <t>91,68; 95,31</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,85; 91,4</t>
+          <t>87,42; 91,2</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,94%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>39,03; 42,33</t>
+          <t>38,75; 42,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>48,51; 52,1</t>
+          <t>48,61; 52,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48,07; 51,51</t>
+          <t>48,05; 51,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38,23; 53,76</t>
+          <t>50,34; 54,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>56,87; 60,2</t>
+          <t>56,82; 60,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>68,7; 71,9</t>
+          <t>68,7; 71,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>63,38; 66,7</t>
+          <t>63,27; 66,59</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>63,1; 71,83</t>
+          <t>61,94; 64,77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>48,47; 50,94</t>
+          <t>48,5; 50,86</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59,37; 61,67</t>
+          <t>59,31; 61,69</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56,3; 58,65</t>
+          <t>56,27; 58,82</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>51,84; 61,58</t>
+          <t>56,79; 59,15</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>99913</t>
+          <t>102521</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>117456</t>
+          <t>139883</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>217369</t>
+          <t>242405</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>81952; 117598</t>
+          <t>81754; 117503</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>107012; 146037</t>
+          <t>105475; 145347</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76018; 111236</t>
+          <t>76746; 111768</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>72002; 133986</t>
+          <t>74457; 130656</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>157248; 198328</t>
+          <t>157380; 196284</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>187939; 229218</t>
+          <t>187747; 230133</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>150690; 188818</t>
+          <t>152053; 190737</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>97650; 141944</t>
+          <t>115280; 166009</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>248718; 301250</t>
+          <t>249695; 305240</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>303722; 363565</t>
+          <t>305835; 363614</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>239272; 291924</t>
+          <t>239613; 291791</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>180543; 258723</t>
+          <t>206515; 283246</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>143654</t>
+          <t>156498</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>271992</t>
+          <t>219305</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>415646</t>
+          <t>375802</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>125890; 169890</t>
+          <t>127337; 168596</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>200519; 253427</t>
+          <t>199963; 248828</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>170300; 216388</t>
+          <t>170263; 214315</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>118989; 170236</t>
+          <t>128859; 182371</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>244260; 295660</t>
+          <t>246846; 296676</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>331783; 381640</t>
+          <t>330299; 380612</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>242982; 290265</t>
+          <t>243790; 291816</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>226998; 369320</t>
+          <t>195602; 242548</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>387101; 454910</t>
+          <t>385010; 456181</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>547929; 616204</t>
+          <t>546873; 620091</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>427961; 493859</t>
+          <t>422928; 492530</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>360376; 548565</t>
+          <t>337353; 411233</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>210309</t>
+          <t>232898</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>272869</t>
+          <t>310083</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>483178</t>
+          <t>542981</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>151285; 196821</t>
+          <t>152262; 196534</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>228638; 280091</t>
+          <t>227341; 279857</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>219262; 271446</t>
+          <t>219572; 270494</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>187455; 235041</t>
+          <t>207167; 259290</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>288395; 341060</t>
+          <t>284475; 337330</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>403490; 458874</t>
+          <t>403975; 458139</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>314422; 365169</t>
+          <t>316561; 364692</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>254736; 292812</t>
+          <t>289206; 332880</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>451994; 524054</t>
+          <t>451499; 521962</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>645963; 722578</t>
+          <t>646850; 723831</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>550972; 626012</t>
+          <t>553236; 621036</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>453616; 518093</t>
+          <t>511942; 576875</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>327224</t>
+          <t>352583</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>420183</t>
+          <t>449254</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>747408</t>
+          <t>801837</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>184061; 228949</t>
+          <t>183103; 229626</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>262114; 317482</t>
+          <t>265255; 315573</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>306326; 361943</t>
+          <t>307849; 362631</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>143183; 463355</t>
+          <t>323133; 379703</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>270304; 312237</t>
+          <t>267403; 314430</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>401164; 450962</t>
+          <t>401771; 449963</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>370205; 421583</t>
+          <t>370465; 421216</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>344491; 448413</t>
+          <t>428978; 471856</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>463043; 533198</t>
+          <t>467703; 531050</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>684538; 756149</t>
+          <t>679803; 755341</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>693641; 769296</t>
+          <t>698096; 768558</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>470664; 901229</t>
+          <t>768409; 835750</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>397403</t>
+          <t>422419</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>409839</t>
+          <t>455890</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>807242</t>
+          <t>878309</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>264866; 297362</t>
+          <t>263545; 298679</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>302758; 340360</t>
+          <t>302849; 342133</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>289597; 333658</t>
+          <t>289603; 332149</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>378275; 416846</t>
+          <t>400749; 445440</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>285917; 319593</t>
+          <t>285458; 320209</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>351533; 387406</t>
+          <t>353836; 387553</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>373372; 413441</t>
+          <t>373515; 414191</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>394139; 423231</t>
+          <t>439402; 472009</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>561867; 609684</t>
+          <t>559780; 610686</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>667860; 719421</t>
+          <t>667153; 718268</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>677593; 738738</t>
+          <t>673243; 731716</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>782471; 830667</t>
+          <t>849643; 905393</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>282870</t>
+          <t>311188</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>540461</t>
+          <t>365907</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>823331</t>
+          <t>677095</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>218554; 244351</t>
+          <t>216967; 244509</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>261592; 284306</t>
+          <t>261593; 283632</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>263278; 292499</t>
+          <t>266400; 293233</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>268013; 294607</t>
+          <t>297080; 326051</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>297109; 318872</t>
+          <t>296006; 317936</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>311942; 334730</t>
+          <t>313479; 334540</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>334022; 356630</t>
+          <t>333080; 356159</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>500725; 577322</t>
+          <t>353072; 376414</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>523316; 557781</t>
+          <t>523244; 558332</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>582903; 614951</t>
+          <t>582886; 614871</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608106; 642258</t>
+          <t>608724; 642840</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>775969; 895782</t>
+          <t>656615; 695398</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>244253</t>
+          <t>267190</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>390151</t>
+          <t>424254</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>634403</t>
+          <t>691444</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>177413; 195150</t>
+          <t>178170; 194859</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>223864; 240338</t>
+          <t>224604; 240333</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>224201; 241180</t>
+          <t>224670; 241795</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>234327; 252603</t>
+          <t>254080; 277204</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>300033; 319997</t>
+          <t>300781; 320149</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>367176; 383489</t>
+          <t>366890; 382498</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>368957; 388723</t>
+          <t>369808; 389101</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>380618; 397712</t>
+          <t>413321; 432740</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>485364; 511344</t>
+          <t>484675; 510687</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>597070; 619491</t>
+          <t>597546; 620127</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>600675; 625974</t>
+          <t>602462; 626335</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>622010; 647174</t>
+          <t>676789; 706077</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1705627</t>
+          <t>1845298</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2422952</t>
+          <t>2364576</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>4128578</t>
+          <t>4209874</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1278406; 1386547</t>
+          <t>1269227; 1384329</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1659947; 1782840</t>
+          <t>1663558; 1785559</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1631591; 1748531</t>
+          <t>1631125; 1744987</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1322592; 1860030</t>
+          <t>1778416; 1909063</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1921725; 2034112</t>
+          <t>1919943; 2033055</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2442542; 2556228</t>
+          <t>2442617; 2556595</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2246478; 2364311</t>
+          <t>2242521; 2360411</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2308673; 2627814</t>
+          <t>2312258; 2418038</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3225281; 3389671</t>
+          <t>3227741; 3384674</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4142304; 4302665</t>
+          <t>4138554; 4304306</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3906636; 4069645</t>
+          <t>3904331; 4081280</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3690438; 4383430</t>
+          <t>4126631; 4298084</t>
         </is>
       </c>
     </row>
